--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008412105359976642</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>8207628</v>
+        <v>4114638</v>
       </c>
       <c r="L2" t="n">
-        <v>3222090</v>
+        <v>1606020</v>
       </c>
       <c r="M2" t="n">
-        <v>571521</v>
+        <v>280111</v>
       </c>
       <c r="N2" t="n">
-        <v>12545</v>
+        <v>6450</v>
       </c>
       <c r="O2" t="n">
-        <v>349731</v>
+        <v>176761</v>
       </c>
       <c r="P2" t="n">
-        <v>7266</v>
+        <v>4386</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.99993497133255</v>
+        <v>0.9998804330825806</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7235547304153442</v>
+        <v>0.7216213345527649</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5298485159873962</v>
+        <v>0.530322790145874</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3997159004211426</v>
+        <v>0.401831328868866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04377073794603348</v>
+        <v>0.04617069661617279</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3995952904224396</v>
+        <v>0.402706116437912</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4498235583305359</v>
+        <v>0.4460943937301636</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,130 +792,130 @@
         <v>0.002017379093236049</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>8207628</v>
+        <v>4114638</v>
       </c>
       <c r="E3" t="n">
-        <v>1774311</v>
+        <v>876664</v>
       </c>
       <c r="F3" t="n">
-        <v>74438</v>
+        <v>34722</v>
       </c>
       <c r="G3" t="n">
-        <v>8509</v>
+        <v>4167</v>
       </c>
       <c r="H3" t="n">
-        <v>7764</v>
+        <v>3684</v>
       </c>
       <c r="I3" t="n">
-        <v>327</v>
+        <v>218</v>
       </c>
       <c r="J3" t="n">
-        <v>20032423</v>
+        <v>10015867</v>
       </c>
       <c r="K3" t="n">
-        <v>19450313</v>
+        <v>9708165</v>
       </c>
       <c r="L3" t="n">
-        <v>23285467</v>
+        <v>11647885</v>
       </c>
       <c r="M3" t="n">
-        <v>29937737</v>
+        <v>14980813</v>
       </c>
       <c r="N3" t="n">
-        <v>32207069</v>
+        <v>16107287</v>
       </c>
       <c r="O3" t="n">
-        <v>31115960</v>
+        <v>15558455</v>
       </c>
       <c r="P3" t="n">
-        <v>32263768</v>
+        <v>16130872</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8148117661476135</v>
+        <v>0.8173471093177795</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4945898950099945</v>
+        <v>0.4927419722080231</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3067472279071808</v>
+        <v>0.3006089329719543</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07045021653175354</v>
+        <v>0.07241982966661453</v>
       </c>
       <c r="V3" t="n">
-        <v>0.343628853559494</v>
+        <v>0.3472895324230194</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01879729330539703</v>
+        <v>0.02269223146140575</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03184710126109398</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>2791311</v>
+        <v>1410210</v>
       </c>
       <c r="E4" t="n">
-        <v>3222090</v>
+        <v>1606020</v>
       </c>
       <c r="F4" t="n">
-        <v>386485</v>
+        <v>186343</v>
       </c>
       <c r="G4" t="n">
-        <v>44885</v>
+        <v>21938</v>
       </c>
       <c r="H4" t="n">
-        <v>68535</v>
+        <v>34074</v>
       </c>
       <c r="I4" t="n">
-        <v>1338</v>
+        <v>750</v>
       </c>
       <c r="J4" t="n">
-        <v>821</v>
+        <v>755</v>
       </c>
       <c r="K4" t="n">
-        <v>3135851</v>
+        <v>1587297</v>
       </c>
       <c r="L4" t="n">
-        <v>2859063</v>
+        <v>1422362</v>
       </c>
       <c r="M4" t="n">
-        <v>858297</v>
+        <v>416975</v>
       </c>
       <c r="N4" t="n">
-        <v>274062</v>
+        <v>133249</v>
       </c>
       <c r="O4" t="n">
-        <v>525482</v>
+        <v>262172</v>
       </c>
       <c r="P4" t="n">
-        <v>8887</v>
+        <v>5446</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999675154685974</v>
+        <v>0.9999402165412903</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7664765119552612</v>
+        <v>0.7665071487426758</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5116124749183655</v>
+        <v>0.5108421444892883</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3471143543720245</v>
+        <v>0.3439269959926605</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05399461090564728</v>
+        <v>0.05639023706316948</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3695048689842224</v>
+        <v>0.3729504942893982</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03608659654855728</v>
+        <v>0.04318756982684135</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>254930</v>
+        <v>130913</v>
       </c>
       <c r="E5" t="n">
-        <v>803132</v>
+        <v>404010</v>
       </c>
       <c r="F5" t="n">
-        <v>571521</v>
+        <v>280111</v>
       </c>
       <c r="G5" t="n">
-        <v>70151</v>
+        <v>34396</v>
       </c>
       <c r="H5" t="n">
-        <v>161323</v>
+        <v>80976</v>
       </c>
       <c r="I5" t="n">
-        <v>1996</v>
+        <v>1306</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1865408</v>
+        <v>919500</v>
       </c>
       <c r="L5" t="n">
-        <v>3292580</v>
+        <v>1653333</v>
       </c>
       <c r="M5" t="n">
-        <v>1291645</v>
+        <v>651701</v>
       </c>
       <c r="N5" t="n">
-        <v>165524</v>
+        <v>82614</v>
       </c>
       <c r="O5" t="n">
-        <v>668027</v>
+        <v>332212</v>
       </c>
       <c r="P5" t="n">
-        <v>379279</v>
+        <v>188896</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999748468399048</v>
+        <v>0.9999537467956543</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8468652367591858</v>
+        <v>0.8464875221252441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8116413354873657</v>
+        <v>0.8116490840911865</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9341704249382019</v>
+        <v>0.9345558881759644</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9865401983261108</v>
+        <v>0.9867808818817139</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9634556770324707</v>
+        <v>0.9636008143424988</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9881146550178528</v>
+        <v>0.9880988001823425</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>45960</v>
+        <v>23463</v>
       </c>
       <c r="E6" t="n">
-        <v>53998</v>
+        <v>26968</v>
       </c>
       <c r="F6" t="n">
-        <v>47969</v>
+        <v>23358</v>
       </c>
       <c r="G6" t="n">
-        <v>12545</v>
+        <v>6450</v>
       </c>
       <c r="H6" t="n">
-        <v>16993</v>
+        <v>8467</v>
       </c>
       <c r="I6" t="n">
-        <v>531</v>
+        <v>298</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D7" t="n">
-        <v>40072</v>
+        <v>20743</v>
       </c>
       <c r="E7" t="n">
-        <v>202546</v>
+        <v>102204</v>
       </c>
       <c r="F7" t="n">
-        <v>298576</v>
+        <v>147327</v>
       </c>
       <c r="G7" t="n">
-        <v>121890</v>
+        <v>58825</v>
       </c>
       <c r="H7" t="n">
-        <v>349731</v>
+        <v>176761</v>
       </c>
       <c r="I7" t="n">
-        <v>4695</v>
+        <v>2874</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D8" t="n">
-        <v>3578</v>
+        <v>1968</v>
       </c>
       <c r="E8" t="n">
-        <v>25076</v>
+        <v>12516</v>
       </c>
       <c r="F8" t="n">
-        <v>50829</v>
+        <v>25225</v>
       </c>
       <c r="G8" t="n">
-        <v>28627</v>
+        <v>13923</v>
       </c>
       <c r="H8" t="n">
-        <v>270867</v>
+        <v>134971</v>
       </c>
       <c r="I8" t="n">
-        <v>7266</v>
+        <v>4386</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
